--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/5_five_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_4_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/5_five_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_4_bus.xlsx
@@ -541,7 +541,7 @@
         <v>1.019485521667526</v>
       </c>
       <c r="G2">
-        <v>-0.03879109617642213</v>
+        <v>-0.03879109617642162</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -561,10 +561,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8902319386646703</v>
+        <v>0.8902319386646702</v>
       </c>
       <c r="G3">
-        <v>-0.7797968923376516</v>
+        <v>-0.779796892337649</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -584,10 +584,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.8453339436572478</v>
+        <v>0.8453339436572476</v>
       </c>
       <c r="G4">
-        <v>1.267200525268436</v>
+        <v>1.267200525268441</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -607,10 +607,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.8453339436718406</v>
+        <v>0.8453339436718403</v>
       </c>
       <c r="G5">
-        <v>1.267200529835314</v>
+        <v>1.267200529835319</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -624,7 +624,7 @@
         <v>27.7477005643891</v>
       </c>
       <c r="D6">
-        <v>0.0007385329100534611</v>
+        <v>0.0007385329100534613</v>
       </c>
       <c r="E6">
         <v>0.006009343834854926</v>
@@ -746,22 +746,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.092677014703406</v>
+        <v>1.092677014703385</v>
       </c>
       <c r="O2">
-        <v>1.069211965323112</v>
+        <v>1.069211965323062</v>
       </c>
       <c r="P2">
-        <v>1.092091632423293</v>
+        <v>1.092091632423271</v>
       </c>
       <c r="Q2">
-        <v>29.2921187229132</v>
+        <v>29.29211872291256</v>
       </c>
       <c r="R2">
-        <v>-90.03597083799265</v>
+        <v>-90.03597083799249</v>
       </c>
       <c r="S2">
-        <v>150.6906508046317</v>
+        <v>150.6906508046328</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -805,22 +805,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.067403369962815</v>
+        <v>1.067403369962787</v>
       </c>
       <c r="O3">
-        <v>0.9387871686732769</v>
+        <v>0.9387871686732149</v>
       </c>
       <c r="P3">
-        <v>1.0565561028636</v>
+        <v>1.056556102863581</v>
       </c>
       <c r="Q3">
-        <v>26.08578028765418</v>
+        <v>26.08578028765332</v>
       </c>
       <c r="R3">
-        <v>-90.73804141973514</v>
+        <v>-90.73804141973433</v>
       </c>
       <c r="S3">
-        <v>153.6258712173451</v>
+        <v>153.6258712173467</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -864,22 +864,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.043533396801535</v>
+        <v>1.043533396801504</v>
       </c>
       <c r="O4">
-        <v>0.89351222090797</v>
+        <v>0.8935122209079078</v>
       </c>
       <c r="P4">
-        <v>1.060763957197498</v>
+        <v>1.060763957197483</v>
       </c>
       <c r="Q4">
-        <v>25.34206720922824</v>
+        <v>25.34206720922741</v>
       </c>
       <c r="R4">
-        <v>-88.77958323307293</v>
+        <v>-88.77958323307151</v>
       </c>
       <c r="S4">
-        <v>155.0979067334709</v>
+        <v>155.0979067334727</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -923,22 +923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.043533396772186</v>
+        <v>1.043533396772155</v>
       </c>
       <c r="O5">
-        <v>0.8935122209233943</v>
+        <v>0.893512220923332</v>
       </c>
       <c r="P5">
-        <v>1.060763957232866</v>
+        <v>1.060763957232851</v>
       </c>
       <c r="Q5">
-        <v>25.34206721041374</v>
+        <v>25.3420672104129</v>
       </c>
       <c r="R5">
-        <v>-88.77958322850606</v>
+        <v>-88.77958322850462</v>
       </c>
       <c r="S5">
-        <v>155.0979067339437</v>
+        <v>155.0979067339455</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -949,55 +949,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>34.99498474368438</v>
+        <v>34.99498474368725</v>
       </c>
       <c r="D6">
-        <v>34.99498474368438</v>
+        <v>34.99498474368725</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>8.081745665248604</v>
+        <v>8.081745665249267</v>
       </c>
       <c r="G6">
-        <v>8.081745665248604</v>
+        <v>8.081745665249267</v>
       </c>
       <c r="H6">
-        <v>0.001989879392998875</v>
+        <v>0.001989879391558382</v>
       </c>
       <c r="I6">
-        <v>0.00585525975936874</v>
+        <v>0.00585525975936955</v>
       </c>
       <c r="J6">
-        <v>0.0007617443451825208</v>
+        <v>0.0007617443451825613</v>
       </c>
       <c r="K6">
-        <v>0.006240294707286868</v>
+        <v>0.006240294707286593</v>
       </c>
       <c r="L6">
-        <v>0.000761744345199202</v>
+        <v>0.0007617443451985185</v>
       </c>
       <c r="M6">
-        <v>0.00624029470727319</v>
+        <v>0.006240294707272753</v>
       </c>
       <c r="N6">
-        <v>0.9526279648080838</v>
+        <v>0.9526279648080219</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9526279648082686</v>
+        <v>0.9526279648083096</v>
       </c>
       <c r="Q6">
-        <v>-7.481772401423735E-12</v>
+        <v>-1.134719549145504E-11</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>-179.9999999999871</v>
+        <v>-179.9999999999827</v>
       </c>
     </row>
   </sheetData>
@@ -1119,7 +1119,7 @@
         <v>1.04997554923967</v>
       </c>
       <c r="Q2">
-        <v>29.9985942634273</v>
+        <v>29.99859426342729</v>
       </c>
       <c r="R2">
         <v>-90.00180143451601</v>
@@ -1178,10 +1178,10 @@
         <v>1.049869387330141</v>
       </c>
       <c r="Q3">
-        <v>29.99269099044334</v>
+        <v>29.99269099044333</v>
       </c>
       <c r="R3">
-        <v>-90.01006399193565</v>
+        <v>-90.01006399193564</v>
       </c>
       <c r="S3">
         <v>150.0022784719106</v>
@@ -1234,10 +1234,10 @@
         <v>1.049703970218128</v>
       </c>
       <c r="P4">
-        <v>1.049843609258966</v>
+        <v>1.049843609258967</v>
       </c>
       <c r="Q4">
-        <v>29.99041181059043</v>
+        <v>29.99041181059042</v>
       </c>
       <c r="R4">
         <v>-90.0103800481253</v>
@@ -1296,10 +1296,10 @@
         <v>1.049843609258999</v>
       </c>
       <c r="Q5">
-        <v>29.9904118105906</v>
+        <v>29.99041181059059</v>
       </c>
       <c r="R5">
-        <v>-90.01038004811959</v>
+        <v>-90.01038004811957</v>
       </c>
       <c r="S5">
         <v>150.0044003598892</v>
@@ -1316,7 +1316,7 @@
         <v>0.05931688229148745</v>
       </c>
       <c r="D6">
-        <v>0.05931688229148746</v>
+        <v>0.05931688229148745</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1328,22 +1328,22 @@
         <v>0.0136986473875176</v>
       </c>
       <c r="H6">
-        <v>0.001966667955940062</v>
+        <v>0.001966667954499568</v>
       </c>
       <c r="I6">
-        <v>0.005624308881969514</v>
+        <v>0.005624308881970548</v>
       </c>
       <c r="J6">
-        <v>0.0007385329100565223</v>
+        <v>0.0007385329100564456</v>
       </c>
       <c r="K6">
-        <v>0.006009343834865071</v>
+        <v>0.00600934383486517</v>
       </c>
       <c r="L6">
-        <v>0.0007385329100696446</v>
+        <v>0.0007385329100691217</v>
       </c>
       <c r="M6">
-        <v>0.006009343834854569</v>
+        <v>0.006009343834854746</v>
       </c>
       <c r="N6">
         <v>1.05012424953462</v>
@@ -1352,10 +1352,10 @@
         <v>1.048584227053751</v>
       </c>
       <c r="P6">
-        <v>1.049167932672646</v>
+        <v>1.049167932672647</v>
       </c>
       <c r="Q6">
-        <v>29.95148164044762</v>
+        <v>29.95148164044761</v>
       </c>
       <c r="R6">
         <v>-90.06031761863277</v>
@@ -1486,7 +1486,7 @@
         <v>29.99859432538236</v>
       </c>
       <c r="R2">
-        <v>-90.00180125156574</v>
+        <v>-90.00180125156575</v>
       </c>
       <c r="S2">
         <v>150.0005051008476</v>
@@ -1660,10 +1660,10 @@
         <v>1.099836247687857</v>
       </c>
       <c r="Q5">
-        <v>29.99041227879371</v>
+        <v>29.99041227879372</v>
       </c>
       <c r="R5">
-        <v>-90.0103788512418</v>
+        <v>-90.01037885124181</v>
       </c>
       <c r="S5">
         <v>150.0044004898188</v>
@@ -1692,22 +1692,22 @@
         <v>0.01435023577954025</v>
       </c>
       <c r="H6">
-        <v>0.001989879392998875</v>
+        <v>0.001989879391558382</v>
       </c>
       <c r="I6">
-        <v>0.00585525975936874</v>
+        <v>0.00585525975936955</v>
       </c>
       <c r="J6">
-        <v>0.0007617443451825208</v>
+        <v>0.0007617443451825613</v>
       </c>
       <c r="K6">
-        <v>0.006240294707286868</v>
+        <v>0.006240294707286593</v>
       </c>
       <c r="L6">
-        <v>0.000761744345199202</v>
+        <v>0.0007617443451985185</v>
       </c>
       <c r="M6">
-        <v>0.00624029470727319</v>
+        <v>0.006240294707272753</v>
       </c>
       <c r="N6">
         <v>1.100135989306258</v>
@@ -1722,7 +1722,7 @@
         <v>29.94963030189167</v>
       </c>
       <c r="R6">
-        <v>-90.06269174365448</v>
+        <v>-90.0626917436545</v>
       </c>
       <c r="S6">
         <v>150.019089617159</v>
@@ -1838,22 +1838,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9433071223204125</v>
+        <v>0.9433071223203854</v>
       </c>
       <c r="O2">
-        <v>0.9202097000245304</v>
+        <v>0.9202097000245562</v>
       </c>
       <c r="P2">
-        <v>0.9419737708740823</v>
+        <v>0.9419737708741619</v>
       </c>
       <c r="Q2">
-        <v>29.19323166508538</v>
+        <v>29.19323166508389</v>
       </c>
       <c r="R2">
-        <v>-90.09512014425034</v>
+        <v>-90.09512014424604</v>
       </c>
       <c r="S2">
-        <v>150.761444834683</v>
+        <v>150.7614448346815</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1897,22 +1897,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9229023361557559</v>
+        <v>0.9229023361557279</v>
       </c>
       <c r="O3">
-        <v>0.8065751372450998</v>
+        <v>0.8065751372451117</v>
       </c>
       <c r="P3">
-        <v>0.9095509716091842</v>
+        <v>0.909550971609259</v>
       </c>
       <c r="Q3">
-        <v>25.90646318836101</v>
+        <v>25.90646318835903</v>
       </c>
       <c r="R3">
-        <v>-91.056274381064</v>
+        <v>-91.05627438105914</v>
       </c>
       <c r="S3">
-        <v>153.6843148702769</v>
+        <v>153.6843148702755</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1956,22 +1956,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8892741182216147</v>
+        <v>0.8892741182215831</v>
       </c>
       <c r="O4">
-        <v>0.7636659323889712</v>
+        <v>0.7636659323889832</v>
       </c>
       <c r="P4">
-        <v>0.9244102643485282</v>
+        <v>0.9244102643486044</v>
       </c>
       <c r="Q4">
-        <v>25.39291889705386</v>
+        <v>25.39291889705173</v>
       </c>
       <c r="R4">
-        <v>-87.09305266723659</v>
+        <v>-87.09305266723105</v>
       </c>
       <c r="S4">
-        <v>155.6364982897652</v>
+        <v>155.6364982897638</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2015,22 +2015,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.889274118196919</v>
+        <v>0.8892741181968875</v>
       </c>
       <c r="O5">
-        <v>0.7636659324123609</v>
+        <v>0.7636659324123731</v>
       </c>
       <c r="P5">
-        <v>0.9244102643819464</v>
+        <v>0.9244102643820225</v>
       </c>
       <c r="Q5">
-        <v>25.39291889852796</v>
+        <v>25.39291889852584</v>
       </c>
       <c r="R5">
-        <v>-87.09305266249962</v>
+        <v>-87.09305266249407</v>
       </c>
       <c r="S5">
-        <v>155.6364982900174</v>
+        <v>155.636498290016</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2041,55 +2041,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>29.83070070818118</v>
+        <v>29.83070070818454</v>
       </c>
       <c r="D6">
-        <v>29.83070070818118</v>
+        <v>29.83070070818454</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>6.889105336249093</v>
+        <v>6.88910533624987</v>
       </c>
       <c r="G6">
-        <v>6.889105336249093</v>
+        <v>6.88910533624987</v>
       </c>
       <c r="H6">
-        <v>0.00335212727522544</v>
+        <v>0.003352127273784943</v>
       </c>
       <c r="I6">
-        <v>0.005870361315570191</v>
+        <v>0.005870361315571266</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479247422</v>
+        <v>0.0009575007479249323</v>
       </c>
       <c r="K6">
-        <v>0.006296894770915111</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479205664</v>
+        <v>0.0009575007479203268</v>
       </c>
       <c r="M6">
-        <v>0.006296894770920034</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.8227241232723549</v>
+        <v>0.8227241232723406</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8227241232721628</v>
+        <v>0.8227241232722232</v>
       </c>
       <c r="Q6">
-        <v>1.519215216532798E-11</v>
+        <v>9.13726153691718E-12</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999999828</v>
+        <v>179.9999999999822</v>
       </c>
     </row>
   </sheetData>
@@ -2202,22 +2202,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8936593665804451</v>
+        <v>0.8936593665804233</v>
       </c>
       <c r="O2">
-        <v>0.8717775983947115</v>
+        <v>0.8717775983947266</v>
       </c>
       <c r="P2">
-        <v>0.8923961915437194</v>
+        <v>0.8923961915437183</v>
       </c>
       <c r="Q2">
-        <v>29.19323166508266</v>
+        <v>29.19323166508389</v>
       </c>
       <c r="R2">
-        <v>-90.09512014424749</v>
+        <v>-90.09512014424604</v>
       </c>
       <c r="S2">
-        <v>150.7614448346822</v>
+        <v>150.7614448346815</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2261,22 +2261,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8743285167992427</v>
+        <v>0.8743285167992176</v>
       </c>
       <c r="O3">
-        <v>0.7641238035783302</v>
+        <v>0.7641238035783328</v>
       </c>
       <c r="P3">
-        <v>0.8616798558262917</v>
+        <v>0.8616798558262869</v>
       </c>
       <c r="Q3">
-        <v>25.90646318835823</v>
+        <v>25.90646318835903</v>
       </c>
       <c r="R3">
-        <v>-91.05627438106072</v>
+        <v>-91.05627438105914</v>
       </c>
       <c r="S3">
-        <v>153.6843148702758</v>
+        <v>153.6843148702755</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2320,22 +2320,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.84247020551635</v>
+        <v>0.8424702055163212</v>
       </c>
       <c r="O4">
         <v>0.7234729784919371</v>
       </c>
       <c r="P4">
-        <v>0.8757570803304491</v>
+        <v>0.8757570803304459</v>
       </c>
       <c r="Q4">
-        <v>25.39291889705096</v>
+        <v>25.39291889705173</v>
       </c>
       <c r="R4">
-        <v>-87.0930526672332</v>
+        <v>-87.09305266723106</v>
       </c>
       <c r="S4">
-        <v>155.636498289764</v>
+        <v>155.6364982897638</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2379,22 +2379,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8424702054929543</v>
+        <v>0.8424702054929254</v>
       </c>
       <c r="O5">
         <v>0.7234729785140959</v>
       </c>
       <c r="P5">
-        <v>0.8757570803621084</v>
+        <v>0.8757570803621053</v>
       </c>
       <c r="Q5">
-        <v>25.39291889852507</v>
+        <v>25.39291889852583</v>
       </c>
       <c r="R5">
-        <v>-87.09305266249622</v>
+        <v>-87.09305266249407</v>
       </c>
       <c r="S5">
-        <v>155.6364982900162</v>
+        <v>155.636498290016</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2405,55 +2405,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>28.26066343477588</v>
+        <v>28.26066343477908</v>
       </c>
       <c r="D6">
-        <v>28.26066343477588</v>
+        <v>28.26066343477908</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>6.526520753870845</v>
+        <v>6.526520753871582</v>
       </c>
       <c r="G6">
-        <v>6.526520753870845</v>
+        <v>6.526520753871582</v>
       </c>
       <c r="H6">
-        <v>0.00335212727522544</v>
+        <v>0.003352127273784943</v>
       </c>
       <c r="I6">
-        <v>0.005870361315570191</v>
+        <v>0.005870361315571266</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479247422</v>
+        <v>0.0009575007479249323</v>
       </c>
       <c r="K6">
-        <v>0.006296894770915111</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479205664</v>
+        <v>0.0009575007479203268</v>
       </c>
       <c r="M6">
-        <v>0.006296894770920034</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.7794228427592722</v>
+        <v>0.7794228427592412</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7794228427591336</v>
+        <v>0.77942284275913</v>
       </c>
       <c r="Q6">
-        <v>1.233083455072108E-11</v>
+        <v>9.134575873405953E-12</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999999793</v>
+        <v>179.9999999999822</v>
       </c>
     </row>
   </sheetData>
@@ -2569,7 +2569,7 @@
         <v>0.9500042913249497</v>
       </c>
       <c r="O2">
-        <v>0.9499584202019975</v>
+        <v>0.9499584202019976</v>
       </c>
       <c r="P2">
         <v>0.949974901008377</v>
@@ -2625,10 +2625,10 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9500274430299676</v>
+        <v>0.9500274430299677</v>
       </c>
       <c r="O3">
-        <v>0.9498076839092946</v>
+        <v>0.9498076839092947</v>
       </c>
       <c r="P3">
         <v>0.9498763823371301</v>
@@ -2687,13 +2687,13 @@
         <v>0.9499838462230713</v>
       </c>
       <c r="O4">
-        <v>0.949687168381849</v>
+        <v>0.9496871683818491</v>
       </c>
       <c r="P4">
-        <v>0.9498597353478829</v>
+        <v>0.9498597353478828</v>
       </c>
       <c r="Q4">
-        <v>29.98966943394201</v>
+        <v>29.98966943394202</v>
       </c>
       <c r="R4">
         <v>-90.0086454085385</v>
@@ -2772,7 +2772,7 @@
         <v>0.05366222753909055</v>
       </c>
       <c r="D6">
-        <v>0.05366222753909054</v>
+        <v>0.05366222753909055</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2781,31 +2781,31 @@
         <v>0.01239276079067008</v>
       </c>
       <c r="G6">
-        <v>0.01239276079067007</v>
+        <v>0.01239276079067008</v>
       </c>
       <c r="H6">
-        <v>0.00335212727522544</v>
+        <v>0.003352127273784943</v>
       </c>
       <c r="I6">
-        <v>0.005870361315570191</v>
+        <v>0.005870361315571266</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479247422</v>
+        <v>0.0009575007479249323</v>
       </c>
       <c r="K6">
-        <v>0.006296894770915111</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479205664</v>
+        <v>0.0009575007479203268</v>
       </c>
       <c r="M6">
-        <v>0.006296894770920034</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
         <v>0.9500940258818807</v>
       </c>
       <c r="O6">
-        <v>0.948623110526077</v>
+        <v>0.9486231105260772</v>
       </c>
       <c r="P6">
         <v>0.9492176836326889</v>
@@ -2930,13 +2930,13 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9000040529173388</v>
+        <v>0.9000040529173385</v>
       </c>
       <c r="O2">
         <v>0.8999605960646216</v>
       </c>
       <c r="P2">
-        <v>0.899976209459921</v>
+        <v>0.8999762094599211</v>
       </c>
       <c r="Q2">
         <v>29.99840273103079</v>
@@ -2992,16 +2992,16 @@
         <v>0.9000259861112604</v>
       </c>
       <c r="O3">
-        <v>0.8998177932629992</v>
+        <v>0.8998177932629994</v>
       </c>
       <c r="P3">
-        <v>0.8998828759831989</v>
+        <v>0.899882875983199</v>
       </c>
       <c r="Q3">
         <v>29.99234777609227</v>
       </c>
       <c r="R3">
-        <v>-90.01052169766038</v>
+        <v>-90.01052169766037</v>
       </c>
       <c r="S3">
         <v>150.0023929725073</v>
@@ -3048,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.899984683873724</v>
+        <v>0.8999846838737239</v>
       </c>
       <c r="O4">
         <v>0.8997036206596426</v>
@@ -3107,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8999846838736677</v>
+        <v>0.8999846838736676</v>
       </c>
       <c r="O5">
-        <v>0.8997036206596055</v>
+        <v>0.8997036206596056</v>
       </c>
       <c r="P5">
         <v>0.8998671051515381</v>
@@ -3119,7 +3119,7 @@
         <v>29.98966943394272</v>
       </c>
       <c r="R5">
-        <v>-90.00864540853159</v>
+        <v>-90.00864540853158</v>
       </c>
       <c r="S5">
         <v>150.0060099969023</v>
@@ -3133,10 +3133,10 @@
         <v>0</v>
       </c>
       <c r="C6">
+        <v>0.0508378990650624</v>
+      </c>
+      <c r="D6">
         <v>0.05083789906506239</v>
-      </c>
-      <c r="D6">
-        <v>0.05083789906506238</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -3148,34 +3148,34 @@
         <v>0.01174051005904675</v>
       </c>
       <c r="H6">
-        <v>0.00335212727522544</v>
+        <v>0.003352127273784943</v>
       </c>
       <c r="I6">
-        <v>0.005870361315570191</v>
+        <v>0.005870361315571266</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479247422</v>
+        <v>0.0009575007479249323</v>
       </c>
       <c r="K6">
-        <v>0.006296894770915111</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479205664</v>
+        <v>0.0009575007479203268</v>
       </c>
       <c r="M6">
-        <v>0.006296894770920034</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.9000890646016673</v>
+        <v>0.900089064601667</v>
       </c>
       <c r="O6">
-        <v>0.8986955658629662</v>
+        <v>0.8986955658629663</v>
       </c>
       <c r="P6">
-        <v>0.8992588456403235</v>
+        <v>0.8992588456403238</v>
       </c>
       <c r="Q6">
-        <v>29.94878109295495</v>
+        <v>29.94878109295496</v>
       </c>
       <c r="R6">
         <v>-90.06109628202213</v>
@@ -3297,22 +3297,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.033845171439842</v>
+        <v>1.033845171440195</v>
       </c>
       <c r="O2">
-        <v>1.049999952317027</v>
+        <v>1.049999952317032</v>
       </c>
       <c r="P2">
-        <v>1.035524990239353</v>
+        <v>1.035524990238299</v>
       </c>
       <c r="Q2">
-        <v>30.41182957608369</v>
+        <v>30.41182957616091</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999575</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S2">
-        <v>149.4301958087111</v>
+        <v>149.4301958087651</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3359,22 +3359,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9636794135924721</v>
+        <v>0.9636794135941192</v>
       </c>
       <c r="O3">
-        <v>1.049999952317396</v>
+        <v>1.0499999523174</v>
       </c>
       <c r="P3">
-        <v>0.9784044573591202</v>
+        <v>0.9784044573531379</v>
       </c>
       <c r="Q3">
-        <v>32.04978637230791</v>
+        <v>32.04978637274323</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999572</v>
+        <v>-89.99999999999632</v>
       </c>
       <c r="S3">
-        <v>146.5982523467893</v>
+        <v>146.5982523470546</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9493517325644686</v>
+        <v>0.9493517325683709</v>
       </c>
       <c r="O4">
-        <v>1.049999952317396</v>
+        <v>1.0499999523174</v>
       </c>
       <c r="P4">
-        <v>0.9466247679715375</v>
+        <v>0.9466247679649218</v>
       </c>
       <c r="Q4">
-        <v>33.75220966783251</v>
+        <v>33.75220966836376</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999569</v>
+        <v>-89.99999999999629</v>
       </c>
       <c r="S4">
-        <v>146.4955921470583</v>
+        <v>146.4955921474816</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3483,22 +3483,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9493517325906777</v>
+        <v>0.9493517325945801</v>
       </c>
       <c r="O5">
-        <v>1.049999952317396</v>
+        <v>1.0499999523174</v>
       </c>
       <c r="P5">
-        <v>0.9466247679535356</v>
+        <v>0.9466247679469199</v>
       </c>
       <c r="Q5">
-        <v>33.75220966967366</v>
+        <v>33.75220967020491</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999569</v>
+        <v>-89.99999999999629</v>
       </c>
       <c r="S5">
-        <v>146.4955921492352</v>
+        <v>146.4955921496584</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3509,7 +3509,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>40.46859745555294</v>
+        <v>40.46859745617393</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -3518,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9.34582239313964</v>
+        <v>9.345822393283054</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -3527,43 +3527,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.001966667955940062</v>
+        <v>0.001966667954499568</v>
       </c>
       <c r="I6">
-        <v>0.005624308881969514</v>
+        <v>0.005624308881970548</v>
       </c>
       <c r="J6">
-        <v>0.0007385329100565223</v>
+        <v>0.0007385329100564456</v>
       </c>
       <c r="K6">
-        <v>0.006009343834865071</v>
+        <v>0.00600934383486517</v>
       </c>
       <c r="L6">
-        <v>0.0007385329100696446</v>
+        <v>0.0007385329100691217</v>
       </c>
       <c r="M6">
-        <v>0.006009343834854569</v>
+        <v>0.006009343834854746</v>
       </c>
       <c r="N6">
-        <v>0.56672164957511</v>
+        <v>0.566721649608698</v>
       </c>
       <c r="O6">
-        <v>1.049999952315629</v>
+        <v>1.049999952315634</v>
       </c>
       <c r="P6">
-        <v>0.641687556176977</v>
+        <v>0.6416875561290677</v>
       </c>
       <c r="Q6">
-        <v>58.2402230663959</v>
+        <v>58.24022307001619</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999577</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S6">
-        <v>117.7015828697557</v>
+        <v>117.701582870713</v>
       </c>
       <c r="T6">
-        <v>40.46859745555295</v>
+        <v>40.46859745617393</v>
       </c>
     </row>
   </sheetData>
@@ -3679,22 +3679,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.083729929363856</v>
+        <v>1.0837299293642</v>
       </c>
       <c r="O2">
-        <v>1.100000023842608</v>
+        <v>1.10000002384261</v>
       </c>
       <c r="P2">
-        <v>1.085360884336326</v>
+        <v>1.08536088433532</v>
       </c>
       <c r="Q2">
-        <v>30.39926664246397</v>
+        <v>30.39926664253502</v>
       </c>
       <c r="R2">
         <v>-89.99999999999633</v>
       </c>
       <c r="S2">
-        <v>149.4542982539175</v>
+        <v>149.4542982539677</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3741,22 +3741,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.013033707692075</v>
+        <v>1.013033707693708</v>
       </c>
       <c r="O3">
-        <v>1.100000023842974</v>
+        <v>1.100000023842976</v>
       </c>
       <c r="P3">
-        <v>1.027496389441505</v>
+        <v>1.027496389435747</v>
       </c>
       <c r="Q3">
-        <v>31.98396847853796</v>
+        <v>31.98396847893925</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999631</v>
+        <v>-89.99999999999632</v>
       </c>
       <c r="S3">
-        <v>146.746997196233</v>
+        <v>146.7469971964812</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3803,22 +3803,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9986303793105007</v>
+        <v>0.9986303793143213</v>
       </c>
       <c r="O4">
-        <v>1.100000023842974</v>
+        <v>1.100000023842977</v>
       </c>
       <c r="P4">
-        <v>0.9954299066830748</v>
+        <v>0.9954299066767263</v>
       </c>
       <c r="Q4">
-        <v>33.61841301364478</v>
+        <v>33.61841301413391</v>
       </c>
       <c r="R4">
         <v>-89.99999999999629</v>
       </c>
       <c r="S4">
-        <v>146.6596764508684</v>
+        <v>146.6596764512627</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3865,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9986303793382327</v>
+        <v>0.9986303793420535</v>
       </c>
       <c r="O5">
-        <v>1.100000023842974</v>
+        <v>1.100000023842976</v>
       </c>
       <c r="P5">
-        <v>0.9954299066642918</v>
+        <v>0.9954299066579432</v>
       </c>
       <c r="Q5">
-        <v>33.61841301549261</v>
+        <v>33.61841301598173</v>
       </c>
       <c r="R5">
         <v>-89.99999999999629</v>
       </c>
       <c r="S5">
-        <v>146.6596764530628</v>
+        <v>146.6596764534572</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>40.82089950229611</v>
+        <v>40.82089950288858</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -3900,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9.4271830669613</v>
+        <v>9.427183067098126</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -3909,43 +3909,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.001989879392998875</v>
+        <v>0.001989879391558382</v>
       </c>
       <c r="I6">
-        <v>0.00585525975936874</v>
+        <v>0.00585525975936955</v>
       </c>
       <c r="J6">
-        <v>0.0007617443451825208</v>
+        <v>0.0007617443451825613</v>
       </c>
       <c r="K6">
-        <v>0.006240294707286868</v>
+        <v>0.006240294707286593</v>
       </c>
       <c r="L6">
-        <v>0.000761744345199202</v>
+        <v>0.0007617443451985185</v>
       </c>
       <c r="M6">
-        <v>0.00624029470727319</v>
+        <v>0.006240294707272753</v>
       </c>
       <c r="N6">
-        <v>0.5951703360416556</v>
+        <v>0.5951703360757895</v>
       </c>
       <c r="O6">
-        <v>1.10000002384291</v>
+        <v>1.100000023842912</v>
       </c>
       <c r="P6">
-        <v>0.6707606260437528</v>
+        <v>0.6707606259955273</v>
       </c>
       <c r="Q6">
-        <v>58.3231048480699</v>
+        <v>58.32310485152149</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S6">
-        <v>117.7717217972161</v>
+        <v>117.7717217981701</v>
       </c>
       <c r="T6">
-        <v>40.82089950229611</v>
+        <v>40.82089950288857</v>
       </c>
     </row>
   </sheetData>
@@ -4132,7 +4132,7 @@
         <v>1.049975878810553</v>
       </c>
       <c r="Q3">
-        <v>29.99907927901631</v>
+        <v>29.9990792790163</v>
       </c>
       <c r="R3">
         <v>-89.99999999999635</v>
@@ -4273,7 +4273,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.0342687643104667</v>
+        <v>0.03426876431046834</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.007914032237705785</v>
+        <v>0.007914032237706163</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -4291,22 +4291,22 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.001966667955940062</v>
+        <v>0.001966667954499568</v>
       </c>
       <c r="I6">
-        <v>0.005624308881969514</v>
+        <v>0.005624308881970548</v>
       </c>
       <c r="J6">
-        <v>0.0007385329100565223</v>
+        <v>0.0007385329100564456</v>
       </c>
       <c r="K6">
-        <v>0.006009343834865071</v>
+        <v>0.00600934383486517</v>
       </c>
       <c r="L6">
-        <v>0.0007385329100696446</v>
+        <v>0.0007385329100691217</v>
       </c>
       <c r="M6">
-        <v>0.006009343834854569</v>
+        <v>0.006009343834854746</v>
       </c>
       <c r="N6">
         <v>1.049486255355817</v>
@@ -4327,7 +4327,7 @@
         <v>149.9737579468331</v>
       </c>
       <c r="T6">
-        <v>0.03426876431046669</v>
+        <v>0.03426876431046834</v>
       </c>
     </row>
   </sheetData>
@@ -4383,7 +4383,7 @@
         <v>1.069211965322762</v>
       </c>
       <c r="G2">
-        <v>-0.03597083799321057</v>
+        <v>-0.03597083799321051</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4406,7 +4406,7 @@
         <v>0.9387871686719225</v>
       </c>
       <c r="G3">
-        <v>-0.7380414197227492</v>
+        <v>-0.7380414197227488</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4452,7 +4452,7 @@
         <v>0.8935122209219969</v>
       </c>
       <c r="G5">
-        <v>1.220416771520689</v>
+        <v>1.220416771520688</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4466,7 +4466,7 @@
         <v>27.99598821218996</v>
       </c>
       <c r="D6">
-        <v>0.0007617443451851989</v>
+        <v>0.0007617443451851982</v>
       </c>
       <c r="E6">
         <v>0.006240294707272939</v>
@@ -4803,7 +4803,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.03589970048429639</v>
+        <v>0.03589970048429812</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -4812,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.008290680818914955</v>
+        <v>0.008290680818915354</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -4821,22 +4821,22 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.001989879392998875</v>
+        <v>0.001989879391558382</v>
       </c>
       <c r="I6">
-        <v>0.00585525975936874</v>
+        <v>0.00585525975936955</v>
       </c>
       <c r="J6">
-        <v>0.0007617443451825208</v>
+        <v>0.0007617443451825613</v>
       </c>
       <c r="K6">
-        <v>0.006240294707286868</v>
+        <v>0.006240294707286593</v>
       </c>
       <c r="L6">
-        <v>0.000761744345199202</v>
+        <v>0.0007617443451985185</v>
       </c>
       <c r="M6">
-        <v>0.00624029470727319</v>
+        <v>0.006240294707272753</v>
       </c>
       <c r="N6">
         <v>1.099441315213294</v>
@@ -4848,7 +4848,7 @@
         <v>1.099788898829521</v>
       </c>
       <c r="Q6">
-        <v>29.9959016690196</v>
+        <v>29.99590166901961</v>
       </c>
       <c r="R6">
         <v>-89.99999999999635</v>
@@ -4857,7 +4857,7 @@
         <v>149.9727438811906</v>
       </c>
       <c r="T6">
-        <v>0.03589970048429639</v>
+        <v>0.03589970048429812</v>
       </c>
     </row>
   </sheetData>
@@ -4973,22 +4973,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9338907398194178</v>
+        <v>0.933890739819484</v>
       </c>
       <c r="O2">
-        <v>0.9499999880786923</v>
+        <v>0.9499999880787373</v>
       </c>
       <c r="P2">
-        <v>0.9369763853695656</v>
+        <v>0.9369763853684764</v>
       </c>
       <c r="Q2">
-        <v>30.3560091364018</v>
+        <v>30.35600913648259</v>
       </c>
       <c r="R2">
-        <v>-89.9999999999969</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S2">
-        <v>149.3233468913222</v>
+        <v>149.3233468913626</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5035,22 +5035,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8709486990913707</v>
+        <v>0.8709486990916165</v>
       </c>
       <c r="O3">
-        <v>0.9499999880795422</v>
+        <v>0.9499999880795872</v>
       </c>
       <c r="P3">
-        <v>0.8913468989366281</v>
+        <v>0.8913468989310888</v>
       </c>
       <c r="Q3">
-        <v>31.57801537976882</v>
+        <v>31.57801538017998</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999687</v>
+        <v>-89.99999999999632</v>
       </c>
       <c r="S3">
-        <v>146.3493609686145</v>
+        <v>146.3493609687951</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5097,22 +5097,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8615673229044468</v>
+        <v>0.8615673229075989</v>
       </c>
       <c r="O4">
-        <v>0.9499999880795422</v>
+        <v>0.9499999880795872</v>
       </c>
       <c r="P4">
-        <v>0.852206468592652</v>
+        <v>0.8522064685868469</v>
       </c>
       <c r="Q4">
-        <v>34.1333448324791</v>
+        <v>34.13334483298738</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999683</v>
+        <v>-89.99999999999628</v>
       </c>
       <c r="S4">
-        <v>146.8064507811166</v>
+        <v>146.806450781508</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5159,22 +5159,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8615673229314547</v>
+        <v>0.8615673229346069</v>
       </c>
       <c r="O5">
-        <v>0.9499999880795422</v>
+        <v>0.9499999880795872</v>
       </c>
       <c r="P5">
-        <v>0.8522064685775066</v>
+        <v>0.8522064685717016</v>
       </c>
       <c r="Q5">
-        <v>34.13334483432097</v>
+        <v>34.13334483482925</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999683</v>
+        <v>-89.99999999999628</v>
       </c>
       <c r="S5">
-        <v>146.8064507835098</v>
+        <v>146.8064507839013</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5185,7 +5185,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>34.27889318480944</v>
+        <v>34.27889318551191</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -5194,7 +5194,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7.916371401071989</v>
+        <v>7.916371401234217</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -5203,43 +5203,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.00335212727522544</v>
+        <v>0.003352127273784943</v>
       </c>
       <c r="I6">
-        <v>0.005870361315570191</v>
+        <v>0.005870361315571266</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479247422</v>
+        <v>0.0009575007479249323</v>
       </c>
       <c r="K6">
-        <v>0.006296894770915111</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479205664</v>
+        <v>0.0009575007479203268</v>
       </c>
       <c r="M6">
-        <v>0.006296894770920034</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.4938218942184726</v>
+        <v>0.4938218942402499</v>
       </c>
       <c r="O6">
-        <v>0.9499999880795779</v>
+        <v>0.9499999880796226</v>
       </c>
       <c r="P6">
-        <v>0.6125299715722985</v>
+        <v>0.6125299715314709</v>
       </c>
       <c r="Q6">
-        <v>55.27650455057029</v>
+        <v>55.276504554598</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999699</v>
+        <v>-89.99999999999643</v>
       </c>
       <c r="S6">
-        <v>117.3371178296446</v>
+        <v>117.3371178299217</v>
       </c>
       <c r="T6">
-        <v>34.27889318480944</v>
+        <v>34.2788931855119</v>
       </c>
     </row>
   </sheetData>
@@ -5355,22 +5355,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8847385832828257</v>
+        <v>0.8847385832828958</v>
       </c>
       <c r="O2">
-        <v>0.8999999761577979</v>
+        <v>0.8999999761578259</v>
       </c>
       <c r="P2">
-        <v>0.88766182639484</v>
+        <v>0.8876618263938153</v>
       </c>
       <c r="Q2">
-        <v>30.35600913640262</v>
+        <v>30.35600913648259</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999689</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S2">
-        <v>149.3233468913214</v>
+        <v>149.3233468913627</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8251092823718537</v>
+        <v>0.8251092823720938</v>
       </c>
       <c r="O3">
-        <v>0.8999999761586031</v>
+        <v>0.8999999761586309</v>
       </c>
       <c r="P3">
-        <v>0.8444338924821364</v>
+        <v>0.8444338924768949</v>
       </c>
       <c r="Q3">
-        <v>31.57801537976971</v>
+        <v>31.57801538017998</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999687</v>
+        <v>-89.99999999999632</v>
       </c>
       <c r="S3">
-        <v>146.3493609686136</v>
+        <v>146.3493609687951</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5479,22 +5479,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8162216629502638</v>
+        <v>0.8162216629532565</v>
       </c>
       <c r="O4">
-        <v>0.8999999761586031</v>
+        <v>0.8999999761586309</v>
       </c>
       <c r="P4">
-        <v>0.8073534853048409</v>
+        <v>0.8073534852993476</v>
       </c>
       <c r="Q4">
-        <v>34.13334483248001</v>
+        <v>34.13334483298738</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999682</v>
+        <v>-89.99999999999628</v>
       </c>
       <c r="S4">
-        <v>146.8064507811156</v>
+        <v>146.806450781508</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5541,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8162216629758503</v>
+        <v>0.8162216629788431</v>
       </c>
       <c r="O5">
-        <v>0.8999999761586031</v>
+        <v>0.8999999761586309</v>
       </c>
       <c r="P5">
-        <v>0.8073534852904924</v>
+        <v>0.8073534852849994</v>
       </c>
       <c r="Q5">
-        <v>34.13334483432187</v>
+        <v>34.13334483482925</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999682</v>
+        <v>-89.99999999999628</v>
       </c>
       <c r="S5">
-        <v>146.8064507835089</v>
+        <v>146.8064507839013</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5567,7 +5567,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>32.47474045914218</v>
+        <v>32.47474045980768</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7.499720170134125</v>
+        <v>7.499720170287815</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -5585,43 +5585,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.00335212727522544</v>
+        <v>0.003352127273784943</v>
       </c>
       <c r="I6">
-        <v>0.005870361315570191</v>
+        <v>0.005870361315571266</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479247422</v>
+        <v>0.0009575007479249323</v>
       </c>
       <c r="K6">
-        <v>0.006296894770915111</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479205664</v>
+        <v>0.0009575007479203268</v>
       </c>
       <c r="M6">
-        <v>0.006296894770920034</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.4678312616841851</v>
+        <v>0.4678312617048174</v>
       </c>
       <c r="O6">
-        <v>0.8999999761586369</v>
+        <v>0.8999999761586646</v>
       </c>
       <c r="P6">
-        <v>0.5802915439250854</v>
+        <v>0.5802915438864059</v>
       </c>
       <c r="Q6">
-        <v>55.27650455057206</v>
+        <v>55.27650455459799</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999699</v>
+        <v>-89.99999999999643</v>
       </c>
       <c r="S6">
-        <v>117.3371178296432</v>
+        <v>117.3371178299217</v>
       </c>
       <c r="T6">
-        <v>32.47474045914218</v>
+        <v>32.47474045980768</v>
       </c>
     </row>
   </sheetData>
@@ -5737,13 +5737,13 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9499846891016936</v>
+        <v>0.9499846891016935</v>
       </c>
       <c r="O2">
         <v>0.9499999880790703</v>
       </c>
       <c r="P2">
-        <v>0.9499944998620111</v>
+        <v>0.949994499862011</v>
       </c>
       <c r="Q2">
         <v>29.9998494908675</v>
@@ -5923,13 +5923,13 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9499010259756766</v>
+        <v>0.9499010259756765</v>
       </c>
       <c r="O5">
         <v>0.949999988079071</v>
       </c>
       <c r="P5">
-        <v>0.9499424802005605</v>
+        <v>0.9499424802005604</v>
       </c>
       <c r="Q5">
         <v>30.00055929820913</v>
@@ -5949,7 +5949,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.03100234297527616</v>
+        <v>0.03100234297527765</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -5958,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.00715968453160153</v>
+        <v>0.007159684531601873</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -5967,22 +5967,22 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.00335212727522544</v>
+        <v>0.003352127273784943</v>
       </c>
       <c r="I6">
-        <v>0.005870361315570191</v>
+        <v>0.005870361315571266</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479247422</v>
+        <v>0.0009575007479249323</v>
       </c>
       <c r="K6">
-        <v>0.006296894770915111</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479205664</v>
+        <v>0.0009575007479203268</v>
       </c>
       <c r="M6">
-        <v>0.006296894770920034</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
         <v>0.9495093417654386</v>
@@ -6003,7 +6003,7 @@
         <v>149.9727262298116</v>
       </c>
       <c r="T6">
-        <v>0.03100234297527616</v>
+        <v>0.03100234297527765</v>
       </c>
     </row>
   </sheetData>
@@ -6125,10 +6125,10 @@
         <v>0.8999999761581413</v>
       </c>
       <c r="P2">
-        <v>0.8999947767946841</v>
+        <v>0.899994776794684</v>
       </c>
       <c r="Q2">
-        <v>29.99984949086749</v>
+        <v>29.9998494908675</v>
       </c>
       <c r="R2">
         <v>-89.99999999999635</v>
@@ -6331,7 +6331,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.02937064030391621</v>
+        <v>0.02937064030391762</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.006782858935367553</v>
+        <v>0.006782858935367877</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -6349,25 +6349,25 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0.00335212727522544</v>
+        <v>0.003352127273784943</v>
       </c>
       <c r="I6">
-        <v>0.005870361315570191</v>
+        <v>0.005870361315571266</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479247422</v>
+        <v>0.0009575007479249323</v>
       </c>
       <c r="K6">
-        <v>0.006296894770915111</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479205664</v>
+        <v>0.0009575007479203268</v>
       </c>
       <c r="M6">
-        <v>0.006296894770920034</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.8995351533411816</v>
+        <v>0.8995351533411817</v>
       </c>
       <c r="O6">
         <v>0.899999976158142</v>
@@ -6385,7 +6385,7 @@
         <v>149.9727262298116</v>
       </c>
       <c r="T6">
-        <v>0.02937064030391621</v>
+        <v>0.02937064030391762</v>
       </c>
     </row>
   </sheetData>
@@ -6501,22 +6501,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.034339901259159</v>
+        <v>1.034339901259307</v>
       </c>
       <c r="O2">
-        <v>1.019485521668259</v>
+        <v>1.019485521668196</v>
       </c>
       <c r="P2">
-        <v>1.035185217467773</v>
+        <v>1.035185217466545</v>
       </c>
       <c r="Q2">
-        <v>29.43266449974164</v>
+        <v>29.43266449982081</v>
       </c>
       <c r="R2">
-        <v>-90.03879109617159</v>
+        <v>-90.03879109617466</v>
       </c>
       <c r="S2">
-        <v>150.4070671762703</v>
+        <v>150.4070671763196</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6563,22 +6563,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9721889591094124</v>
+        <v>0.9721889591093009</v>
       </c>
       <c r="O3">
-        <v>0.8902319386665236</v>
+        <v>0.8902319386664571</v>
       </c>
       <c r="P3">
-        <v>0.9707265174784239</v>
+        <v>0.9707265174721283</v>
       </c>
       <c r="Q3">
-        <v>26.57445530856355</v>
+        <v>26.57445530900939</v>
       </c>
       <c r="R3">
-        <v>-90.77979689234022</v>
+        <v>-90.779796892343</v>
       </c>
       <c r="S3">
-        <v>152.0332747648388</v>
+        <v>152.0332747650947</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6625,22 +6625,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9386717781257052</v>
+        <v>0.9386717781271634</v>
       </c>
       <c r="O4">
-        <v>0.8453339436591347</v>
+        <v>0.8453339436590686</v>
       </c>
       <c r="P4">
-        <v>0.9581537155721302</v>
+        <v>0.9581537155652844</v>
       </c>
       <c r="Q4">
-        <v>26.54429276204278</v>
+        <v>26.54429276262907</v>
       </c>
       <c r="R4">
-        <v>-88.73279947474639</v>
+        <v>-88.73279947474882</v>
       </c>
       <c r="S4">
-        <v>153.6256478235302</v>
+        <v>153.6256478239486</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6687,22 +6687,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9386717781082686</v>
+        <v>0.9386717781097269</v>
       </c>
       <c r="O5">
-        <v>0.8453339436737273</v>
+        <v>0.8453339436736613</v>
       </c>
       <c r="P5">
-        <v>0.9581537155972776</v>
+        <v>0.9581537155904316</v>
       </c>
       <c r="Q5">
-        <v>26.54429276439921</v>
+        <v>26.5442927649855</v>
       </c>
       <c r="R5">
-        <v>-88.7327994701795</v>
+        <v>-88.73279947018193</v>
       </c>
       <c r="S5">
-        <v>153.6256478251866</v>
+        <v>153.625647825605</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6716,58 +6716,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>42.62324397953446</v>
+        <v>42.62324397749389</v>
       </c>
       <c r="D6">
-        <v>37.64373316230535</v>
+        <v>37.64373316553878</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>9.843416700806063</v>
+        <v>9.843416700334814</v>
       </c>
       <c r="G6">
-        <v>8.693447919366241</v>
+        <v>8.693447920112972</v>
       </c>
       <c r="H6">
-        <v>0.001966667955940062</v>
+        <v>0.001966667954499568</v>
       </c>
       <c r="I6">
-        <v>0.005624308881969514</v>
+        <v>0.005624308881970548</v>
       </c>
       <c r="J6">
-        <v>0.0007385329100565223</v>
+        <v>0.0007385329100564456</v>
       </c>
       <c r="K6">
-        <v>0.006009343834865071</v>
+        <v>0.00600934383486517</v>
       </c>
       <c r="L6">
-        <v>0.0007385329100696446</v>
+        <v>0.0007385329100691217</v>
       </c>
       <c r="M6">
-        <v>0.006009343834854569</v>
+        <v>0.006009343834854746</v>
       </c>
       <c r="N6">
-        <v>0.6060680162184863</v>
+        <v>0.6060680161956801</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.6060680162198842</v>
+        <v>0.6060680161971177</v>
       </c>
       <c r="Q6">
-        <v>-4.125965121751726</v>
+        <v>-4.12596511758882</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>175.8740348782933</v>
+        <v>175.8740348824648</v>
       </c>
       <c r="T6">
-        <v>40.68771620006072</v>
+        <v>40.68771620176562</v>
       </c>
     </row>
   </sheetData>
@@ -6883,22 +6883,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.084206897673313</v>
+        <v>1.084206897673504</v>
       </c>
       <c r="O2">
-        <v>1.069211965323488</v>
+        <v>1.069211965323453</v>
       </c>
       <c r="P2">
-        <v>1.085028562413883</v>
+        <v>1.085028562412695</v>
       </c>
       <c r="Q2">
-        <v>29.45695330408895</v>
+        <v>29.45695330416265</v>
       </c>
       <c r="R2">
-        <v>-90.0359708379866</v>
+        <v>-90.03597083799106</v>
       </c>
       <c r="S2">
-        <v>150.3944842973883</v>
+        <v>150.3944842974342</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6945,22 +6945,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.021439550115337</v>
+        <v>1.021439550115365</v>
       </c>
       <c r="O3">
-        <v>0.9387871686738446</v>
+        <v>0.9387871686738005</v>
       </c>
       <c r="P3">
-        <v>1.01986423680954</v>
+        <v>1.01986423680346</v>
       </c>
       <c r="Q3">
-        <v>26.72768700350614</v>
+        <v>26.72768700391865</v>
       </c>
       <c r="R3">
-        <v>-90.73804141972073</v>
+        <v>-90.73804141972549</v>
       </c>
       <c r="S3">
-        <v>151.9669768908754</v>
+        <v>151.9669768911153</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7007,22 +7007,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.987690578186287</v>
+        <v>0.9876905781878685</v>
       </c>
       <c r="O4">
-        <v>0.8935122209085642</v>
+        <v>0.8935122209085157</v>
       </c>
       <c r="P4">
-        <v>1.007156369797192</v>
+        <v>1.007156369790596</v>
       </c>
       <c r="Q4">
-        <v>26.7085134502159</v>
+        <v>26.70851345075609</v>
       </c>
       <c r="R4">
-        <v>-88.77958323305606</v>
+        <v>-88.77958323306065</v>
       </c>
       <c r="S4">
-        <v>153.5000433574106</v>
+        <v>153.5000433578005</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7069,22 +7069,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9876905781681045</v>
+        <v>0.987690578169686</v>
       </c>
       <c r="O5">
-        <v>0.8935122209239885</v>
+        <v>0.8935122209239402</v>
       </c>
       <c r="P5">
-        <v>1.007156369823837</v>
+        <v>1.007156369817241</v>
       </c>
       <c r="Q5">
-        <v>26.70851345258355</v>
+        <v>26.70851345312373</v>
       </c>
       <c r="R5">
-        <v>-88.77958322848917</v>
+        <v>-88.77958322849378</v>
       </c>
       <c r="S5">
-        <v>153.5000433590807</v>
+        <v>153.5000433594706</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7098,58 +7098,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>42.91530683091081</v>
+        <v>42.91530682890674</v>
       </c>
       <c r="D6">
-        <v>38.07903534598023</v>
+        <v>38.07903534911816</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>9.910865728156104</v>
+        <v>9.910865727693281</v>
       </c>
       <c r="G6">
-        <v>8.793976654033646</v>
+        <v>8.793976654758319</v>
       </c>
       <c r="H6">
-        <v>0.001989879392998875</v>
+        <v>0.001989879391558382</v>
       </c>
       <c r="I6">
-        <v>0.00585525975936874</v>
+        <v>0.00585525975936955</v>
       </c>
       <c r="J6">
-        <v>0.0007617443451825208</v>
+        <v>0.0007617443451825613</v>
       </c>
       <c r="K6">
-        <v>0.006240294707286868</v>
+        <v>0.006240294707286593</v>
       </c>
       <c r="L6">
-        <v>0.000761744345199202</v>
+        <v>0.0007617443451985185</v>
       </c>
       <c r="M6">
-        <v>0.00624029470727319</v>
+        <v>0.006240294707272753</v>
       </c>
       <c r="N6">
-        <v>0.6346057460959389</v>
+        <v>0.6346057460735788</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.6346057460972185</v>
+        <v>0.6346057460748238</v>
       </c>
       <c r="Q6">
-        <v>-3.973958594570126</v>
+        <v>-3.973958590533219</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>176.0260414054206</v>
+        <v>176.0260414094675</v>
       </c>
       <c r="T6">
-        <v>41.04725517861336</v>
+        <v>41.04725518023615</v>
       </c>
     </row>
   </sheetData>
@@ -7480,37 +7480,37 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.03427084010589073</v>
+        <v>0.03427084010589013</v>
       </c>
       <c r="D6">
-        <v>0.03426764993498414</v>
+        <v>0.03426764993498639</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.007914511622131666</v>
+        <v>0.007914511622131529</v>
       </c>
       <c r="G6">
-        <v>0.007913774883708017</v>
+        <v>0.007913774883708535</v>
       </c>
       <c r="H6">
-        <v>0.001966667955940062</v>
+        <v>0.001966667954499568</v>
       </c>
       <c r="I6">
-        <v>0.005624308881969514</v>
+        <v>0.005624308881970548</v>
       </c>
       <c r="J6">
-        <v>0.0007385329100565223</v>
+        <v>0.0007385329100564456</v>
       </c>
       <c r="K6">
-        <v>0.006009343834865071</v>
+        <v>0.00600934383486517</v>
       </c>
       <c r="L6">
-        <v>0.0007385329100696446</v>
+        <v>0.0007385329100691217</v>
       </c>
       <c r="M6">
-        <v>0.006009343834854569</v>
+        <v>0.006009343834854746</v>
       </c>
       <c r="N6">
         <v>1.049805458058085</v>
@@ -7522,7 +7522,7 @@
         <v>1.049486268380331</v>
       </c>
       <c r="Q6">
-        <v>29.97375638430449</v>
+        <v>29.97375638430448</v>
       </c>
       <c r="R6">
         <v>-90.03017915474202</v>
@@ -7531,7 +7531,7 @@
         <v>149.9960768048021</v>
       </c>
       <c r="T6">
-        <v>0.03426780276895484</v>
+        <v>0.03426780276895812</v>
       </c>
     </row>
   </sheetData>
@@ -7862,37 +7862,37 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.03590187501484356</v>
+        <v>0.03590187501484294</v>
       </c>
       <c r="D6">
-        <v>0.0358985330644493</v>
+        <v>0.03589853306445166</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.008291183005241145</v>
+        <v>0.008291183005241001</v>
       </c>
       <c r="G6">
-        <v>0.008290411214845748</v>
+        <v>0.008290411214846293</v>
       </c>
       <c r="H6">
-        <v>0.001989879392998875</v>
+        <v>0.001989879391558382</v>
       </c>
       <c r="I6">
-        <v>0.00585525975936874</v>
+        <v>0.00585525975936955</v>
       </c>
       <c r="J6">
-        <v>0.0007617443451825208</v>
+        <v>0.0007617443451825613</v>
       </c>
       <c r="K6">
-        <v>0.006240294707286868</v>
+        <v>0.006240294707286593</v>
       </c>
       <c r="L6">
-        <v>0.000761744345199202</v>
+        <v>0.0007617443451985185</v>
       </c>
       <c r="M6">
-        <v>0.00624029470727319</v>
+        <v>0.006240294707272753</v>
       </c>
       <c r="N6">
         <v>1.099788884699155</v>
@@ -7904,7 +7904,7 @@
         <v>1.099441329356045</v>
       </c>
       <c r="Q6">
-        <v>29.97274225826049</v>
+        <v>29.9727422582605</v>
       </c>
       <c r="R6">
         <v>-90.03136781435381</v>
@@ -7913,7 +7913,7 @@
         <v>149.9959032923519</v>
       </c>
       <c r="T6">
-        <v>0.03589869324623296</v>
+        <v>0.0358986932462364</v>
       </c>
     </row>
   </sheetData>
@@ -8029,22 +8029,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9350925986743452</v>
+        <v>0.9350925986741025</v>
       </c>
       <c r="O2">
-        <v>0.9202097000242523</v>
+        <v>0.9202097000243163</v>
       </c>
       <c r="P2">
-        <v>0.936218479880604</v>
+        <v>0.9362184798794412</v>
       </c>
       <c r="Q2">
-        <v>29.29922573323219</v>
+        <v>29.29922573330895</v>
       </c>
       <c r="R2">
-        <v>-90.09512014424591</v>
+        <v>-90.09512014424564</v>
       </c>
       <c r="S2">
-        <v>150.3884534496937</v>
+        <v>150.3884534497172</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8091,22 +8091,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8824833627298417</v>
+        <v>0.8824833627280755</v>
       </c>
       <c r="O3">
-        <v>0.806575137245228</v>
+        <v>0.8065751372452856</v>
       </c>
       <c r="P3">
-        <v>0.882131206322489</v>
+        <v>0.882131206316819</v>
       </c>
       <c r="Q3">
-        <v>26.16500470351562</v>
+        <v>26.16500470388835</v>
       </c>
       <c r="R3">
-        <v>-91.0562743810566</v>
+        <v>-91.05627438105661</v>
       </c>
       <c r="S3">
-        <v>151.7669457446302</v>
+        <v>151.7669457447506</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8153,22 +8153,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8398660845059539</v>
+        <v>0.8398660845060976</v>
       </c>
       <c r="O4">
-        <v>0.763665932389116</v>
+        <v>0.7636659323891686</v>
       </c>
       <c r="P4">
-        <v>0.8768035301479382</v>
+        <v>0.876803530141723</v>
       </c>
       <c r="Q4">
-        <v>26.81081577387778</v>
+        <v>26.81081577441973</v>
       </c>
       <c r="R4">
-        <v>-87.09305266722815</v>
+        <v>-87.09305266722832</v>
       </c>
       <c r="S4">
-        <v>154.0363734854485</v>
+        <v>154.0363734857669</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8215,22 +8215,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8398660844912683</v>
+        <v>0.8398660844914121</v>
       </c>
       <c r="O5">
-        <v>0.7636659324125054</v>
+        <v>0.7636659324125582</v>
       </c>
       <c r="P5">
-        <v>0.876803530173852</v>
+        <v>0.8768035301676368</v>
       </c>
       <c r="Q5">
-        <v>26.81081577660099</v>
+        <v>26.81081577714293</v>
       </c>
       <c r="R5">
-        <v>-87.09305266249116</v>
+        <v>-87.09305266249133</v>
       </c>
       <c r="S5">
-        <v>154.036373486916</v>
+        <v>154.0363734872344</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8244,58 +8244,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>37.68913274083853</v>
+        <v>37.68913273971784</v>
       </c>
       <c r="D6">
-        <v>30.38499303761876</v>
+        <v>30.38499304007867</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>8.703932503077366</v>
+        <v>8.703932502818553</v>
       </c>
       <c r="G6">
-        <v>7.017113668400778</v>
+        <v>7.017113668968871</v>
       </c>
       <c r="H6">
-        <v>0.00335212727522544</v>
+        <v>0.003352127273784943</v>
       </c>
       <c r="I6">
-        <v>0.005870361315570191</v>
+        <v>0.005870361315571266</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479247422</v>
+        <v>0.0009575007479249323</v>
       </c>
       <c r="K6">
-        <v>0.006296894770915111</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479205664</v>
+        <v>0.0009575007479203268</v>
       </c>
       <c r="M6">
-        <v>0.006296894770920034</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.5675888564806811</v>
+        <v>0.5675888564533352</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.5675888564808989</v>
+        <v>0.5675888564535216</v>
       </c>
       <c r="Q6">
-        <v>-6.713373449126904</v>
+        <v>-6.713373446278564</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>173.2866265508017</v>
+        <v>173.2866265536489</v>
       </c>
       <c r="T6">
-        <v>33.58502997378515</v>
+        <v>33.58502997571439</v>
       </c>
     </row>
   </sheetData>
@@ -8351,7 +8351,7 @@
         <v>1.049979730265621</v>
       </c>
       <c r="G2">
-        <v>-0.000901888246122816</v>
+        <v>-0.0009018882461228146</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8374,7 +8374,7 @@
         <v>1.049898497017663</v>
       </c>
       <c r="G3">
-        <v>-0.005037818120266383</v>
+        <v>-0.005037818120266377</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8397,7 +8397,7 @@
         <v>1.049851907180983</v>
       </c>
       <c r="G4">
-        <v>-0.005197044997986881</v>
+        <v>-0.005197044997986874</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8420,7 +8420,7 @@
         <v>1.049851907180956</v>
       </c>
       <c r="G5">
-        <v>-0.005197044995118756</v>
+        <v>-0.005197044995118749</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -8434,7 +8434,7 @@
         <v>0.02374276285742373</v>
       </c>
       <c r="D6">
-        <v>0.0007385329100534611</v>
+        <v>0.0007385329100534613</v>
       </c>
       <c r="E6">
         <v>0.006009343834854926</v>
@@ -8559,22 +8559,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8858771863926659</v>
+        <v>0.8858771863924488</v>
       </c>
       <c r="O2">
-        <v>0.8717775983944579</v>
+        <v>0.8717775983944994</v>
       </c>
       <c r="P2">
-        <v>0.8869438106784971</v>
+        <v>0.8869438106773719</v>
       </c>
       <c r="Q2">
-        <v>29.29922573323215</v>
+        <v>29.29922573330895</v>
       </c>
       <c r="R2">
-        <v>-90.09512014424439</v>
+        <v>-90.09512014424564</v>
       </c>
       <c r="S2">
-        <v>150.3884534496926</v>
+        <v>150.3884534497172</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8621,22 +8621,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8360368582980404</v>
+        <v>0.83603685829638</v>
       </c>
       <c r="O3">
-        <v>0.764123803578462</v>
+        <v>0.7641238035784976</v>
       </c>
       <c r="P3">
-        <v>0.8357032364431307</v>
+        <v>0.8357032364377359</v>
       </c>
       <c r="Q3">
-        <v>26.16500470351552</v>
+        <v>26.16500470388835</v>
       </c>
       <c r="R3">
-        <v>-91.05627438105483</v>
+        <v>-91.05627438105661</v>
       </c>
       <c r="S3">
-        <v>151.766945744629</v>
+        <v>151.7669457447506</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8683,22 +8683,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7956625952804376</v>
+        <v>0.7956625952805865</v>
       </c>
       <c r="O4">
-        <v>0.723472978492083</v>
+        <v>0.7234729784921127</v>
       </c>
       <c r="P4">
-        <v>0.8306559643481384</v>
+        <v>0.8306559643422274</v>
       </c>
       <c r="Q4">
-        <v>26.8108157738777</v>
+        <v>26.81081577441974</v>
       </c>
       <c r="R4">
-        <v>-87.09305266722637</v>
+        <v>-87.09305266722832</v>
       </c>
       <c r="S4">
-        <v>154.0363734854473</v>
+        <v>154.0363734857669</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8745,22 +8745,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7956625952665248</v>
+        <v>0.7956625952666739</v>
       </c>
       <c r="O5">
-        <v>0.7234729785142417</v>
+        <v>0.7234729785142713</v>
       </c>
       <c r="P5">
-        <v>0.8306559643726883</v>
+        <v>0.8306559643667775</v>
       </c>
       <c r="Q5">
-        <v>26.8108157766009</v>
+        <v>26.81081577714293</v>
       </c>
       <c r="R5">
-        <v>-87.09305266248938</v>
+        <v>-87.09305266249133</v>
       </c>
       <c r="S5">
-        <v>154.0363734869147</v>
+        <v>154.0363734872344</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8774,58 +8774,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>35.70549367770356</v>
+        <v>35.70549367664185</v>
       </c>
       <c r="D6">
-        <v>28.78578247639523</v>
+        <v>28.78578247872566</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>8.245830677420704</v>
+        <v>8.245830677175512</v>
       </c>
       <c r="G6">
-        <v>6.647791803692136</v>
+        <v>6.647791804230327</v>
       </c>
       <c r="H6">
-        <v>0.00335212727522544</v>
+        <v>0.003352127273784943</v>
       </c>
       <c r="I6">
-        <v>0.005870361315570191</v>
+        <v>0.005870361315571266</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479247422</v>
+        <v>0.0009575007479249323</v>
       </c>
       <c r="K6">
-        <v>0.006296894770915111</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479205664</v>
+        <v>0.0009575007479203268</v>
       </c>
       <c r="M6">
-        <v>0.006296894770920034</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.537715751274002</v>
+        <v>0.5377157512481054</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.537715751274234</v>
+        <v>0.537715751248282</v>
       </c>
       <c r="Q6">
-        <v>-6.713373449127772</v>
+        <v>-6.713373446278551</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>173.2866265507991</v>
+        <v>173.2866265536489</v>
       </c>
       <c r="T6">
-        <v>31.81739637365268</v>
+        <v>31.81739637548038</v>
       </c>
     </row>
   </sheetData>
@@ -9009,13 +9009,13 @@
         <v>0.9499038087630122</v>
       </c>
       <c r="P3">
-        <v>0.9499266961936816</v>
+        <v>0.9499266961936815</v>
       </c>
       <c r="Q3">
         <v>29.99569160946933</v>
       </c>
       <c r="R3">
-        <v>-90.00526722363973</v>
+        <v>-90.00526722363975</v>
       </c>
       <c r="S3">
         <v>149.9990413223123</v>
@@ -9065,7 +9065,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9499424744247884</v>
+        <v>0.9499424744247885</v>
       </c>
       <c r="O4">
         <v>0.9498435003064293</v>
@@ -9074,7 +9074,7 @@
         <v>0.9499010317522317</v>
       </c>
       <c r="Q4">
-        <v>29.99510982432656</v>
+        <v>29.99510982432657</v>
       </c>
       <c r="R4">
         <v>-90.00433015760096</v>
@@ -9133,7 +9133,7 @@
         <v>0.9498435003064096</v>
       </c>
       <c r="P5">
-        <v>0.9499010317522387</v>
+        <v>0.9499010317522386</v>
       </c>
       <c r="Q5">
         <v>29.99510982432795</v>
@@ -9156,40 +9156,40 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.03100588192094132</v>
+        <v>0.03100588192094078</v>
       </c>
       <c r="D6">
-        <v>0.03100083487760274</v>
+        <v>0.03100083487760477</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.00716050181610668</v>
+        <v>0.007160501816106554</v>
       </c>
       <c r="G6">
-        <v>0.007159336251357254</v>
+        <v>0.007159336251357723</v>
       </c>
       <c r="H6">
-        <v>0.00335212727522544</v>
+        <v>0.003352127273784943</v>
       </c>
       <c r="I6">
-        <v>0.005870361315570191</v>
+        <v>0.005870361315571266</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479247422</v>
+        <v>0.0009575007479249323</v>
       </c>
       <c r="K6">
-        <v>0.006296894770915111</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479205664</v>
+        <v>0.0009575007479203268</v>
       </c>
       <c r="M6">
-        <v>0.006296894770920034</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
-        <v>0.9498018798723483</v>
+        <v>0.9498018798723484</v>
       </c>
       <c r="O6">
         <v>0.9493111849763776</v>
@@ -9207,7 +9207,7 @@
         <v>149.996719585402</v>
       </c>
       <c r="T6">
-        <v>0.03100031200996448</v>
+        <v>0.03100031200996746</v>
       </c>
     </row>
   </sheetData>
@@ -9332,7 +9332,7 @@
         <v>0.8999854828501591</v>
       </c>
       <c r="Q2">
-        <v>29.99912555507401</v>
+        <v>29.999125555074</v>
       </c>
       <c r="R2">
         <v>-90.00102481525582</v>
@@ -9388,7 +9388,7 @@
         <v>0.8999783059418041</v>
       </c>
       <c r="O3">
-        <v>0.8999088589126198</v>
+        <v>0.89990885891262</v>
       </c>
       <c r="P3">
         <v>0.8999305417413728</v>
@@ -9397,7 +9397,7 @@
         <v>29.99569160946933</v>
       </c>
       <c r="R3">
-        <v>-90.00526722363973</v>
+        <v>-90.00526722363975</v>
       </c>
       <c r="S3">
         <v>149.9990413223123</v>
@@ -9512,7 +9512,7 @@
         <v>0.89994548953903</v>
       </c>
       <c r="O5">
-        <v>0.8998517245861087</v>
+        <v>0.8998517245861088</v>
       </c>
       <c r="P5">
         <v>0.8999062280603447</v>
@@ -9538,37 +9538,37 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.02937399298923647</v>
+        <v>0.02937399298923595</v>
       </c>
       <c r="D6">
-        <v>0.02936921157982447</v>
+        <v>0.0293692115798264</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.006783633204887952</v>
+        <v>0.006783633204887833</v>
       </c>
       <c r="G6">
-        <v>0.006782528985667049</v>
+        <v>0.006782528985667494</v>
       </c>
       <c r="H6">
-        <v>0.00335212727522544</v>
+        <v>0.003352127273784943</v>
       </c>
       <c r="I6">
-        <v>0.005870361315570191</v>
+        <v>0.005870361315571266</v>
       </c>
       <c r="J6">
-        <v>0.0009575007479247422</v>
+        <v>0.0009575007479249323</v>
       </c>
       <c r="K6">
-        <v>0.006296894770915111</v>
+        <v>0.006296894770914634</v>
       </c>
       <c r="L6">
-        <v>0.0009575007479205664</v>
+        <v>0.0009575007479203268</v>
       </c>
       <c r="M6">
-        <v>0.006296894770920034</v>
+        <v>0.006296894770919595</v>
       </c>
       <c r="N6">
         <v>0.8998122947017585</v>
@@ -9589,7 +9589,7 @@
         <v>149.996719585402</v>
       </c>
       <c r="T6">
-        <v>0.02936871623154251</v>
+        <v>0.02936871623154532</v>
       </c>
     </row>
   </sheetData>
@@ -9645,7 +9645,7 @@
         <v>1.099978839014074</v>
       </c>
       <c r="G2">
-        <v>-0.0009018424366363309</v>
+        <v>-0.0009018424366363299</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9668,7 +9668,7 @@
         <v>1.099893738025533</v>
       </c>
       <c r="G3">
-        <v>-0.005037575241080466</v>
+        <v>-0.005037575241080462</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9691,7 +9691,7 @@
         <v>1.099844930798715</v>
       </c>
       <c r="G4">
-        <v>-0.005196745313343396</v>
+        <v>-0.00519674531334339</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9714,7 +9714,7 @@
         <v>1.099844930798685</v>
       </c>
       <c r="G5">
-        <v>-0.00519674531033874</v>
+        <v>-0.005196745310338735</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9728,7 +9728,7 @@
         <v>0.02487274025906318</v>
       </c>
       <c r="D6">
-        <v>0.0007617443451851989</v>
+        <v>0.0007617443451851982</v>
       </c>
       <c r="E6">
         <v>0.006240294707272939</v>
@@ -9793,7 +9793,7 @@
         <v>0.9202097000230514</v>
       </c>
       <c r="G2">
-        <v>-0.09512014424988315</v>
+        <v>-0.09512014424988387</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9813,10 +9813,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.80657513724449</v>
+        <v>0.8065751372444899</v>
       </c>
       <c r="G3">
-        <v>-1.056274381063369</v>
+        <v>-1.056274381063373</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9836,10 +9836,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.7636659323883898</v>
+        <v>0.7636659323883896</v>
       </c>
       <c r="G4">
-        <v>2.906947332764131</v>
+        <v>2.906947332764127</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9859,10 +9859,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7636659324117794</v>
+        <v>0.7636659324117793</v>
       </c>
       <c r="G5">
-        <v>2.906947337501114</v>
+        <v>2.906947337501111</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9870,16 +9870,16 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>34.44552616794237</v>
+        <v>34.44552616794238</v>
       </c>
       <c r="C6">
-        <v>23.86456092213745</v>
+        <v>23.86456092213746</v>
       </c>
       <c r="D6">
-        <v>0.0009575007479215066</v>
+        <v>0.0009575007479215064</v>
       </c>
       <c r="E6">
-        <v>0.006296894770919785</v>
+        <v>0.006296894770919784</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -9941,7 +9941,7 @@
         <v>0.8717775983933012</v>
       </c>
       <c r="G2">
-        <v>-0.09512014424988338</v>
+        <v>-0.09512014424988388</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9964,7 +9964,7 @@
         <v>0.764123803577744</v>
       </c>
       <c r="G3">
-        <v>-1.05627438106337</v>
+        <v>-1.056274381063373</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9984,10 +9984,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.7234729784913748</v>
+        <v>0.7234729784913747</v>
       </c>
       <c r="G4">
-        <v>2.90694733276413</v>
+        <v>2.906947332764127</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10007,10 +10007,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7234729785135334</v>
+        <v>0.7234729785135333</v>
       </c>
       <c r="G5">
-        <v>2.906947337501113</v>
+        <v>2.90694733750111</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10018,16 +10018,16 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>32.63260328306709</v>
+        <v>32.6326032830671</v>
       </c>
       <c r="C6">
         <v>22.60853108469782</v>
       </c>
       <c r="D6">
-        <v>0.0009575007479215066</v>
+        <v>0.0009575007479215064</v>
       </c>
       <c r="E6">
-        <v>0.006296894770919785</v>
+        <v>0.006296894770919784</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -10112,7 +10112,7 @@
         <v>0.9499038087630096</v>
       </c>
       <c r="G3">
-        <v>-0.005267223643389584</v>
+        <v>-0.005267223643389585</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10135,7 +10135,7 @@
         <v>0.9498435003064266</v>
       </c>
       <c r="G4">
-        <v>-0.004330157604604892</v>
+        <v>-0.004330157604604893</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10158,7 +10158,7 @@
         <v>0.9498435003064071</v>
       </c>
       <c r="G5">
-        <v>-0.004330157601146439</v>
+        <v>-0.004330157601146441</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10172,10 +10172,10 @@
         <v>0.02148046068346462</v>
       </c>
       <c r="D6">
-        <v>0.0009575007479215066</v>
+        <v>0.0009575007479215064</v>
       </c>
       <c r="E6">
-        <v>0.006296894770919785</v>
+        <v>0.006296894770919784</v>
       </c>
       <c r="F6">
         <v>0.9493111849763752</v>
@@ -10260,7 +10260,7 @@
         <v>0.8999088589126175</v>
       </c>
       <c r="G3">
-        <v>-0.005267223643389584</v>
+        <v>-0.005267223643389587</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10283,7 +10283,7 @@
         <v>0.8998517245861249</v>
       </c>
       <c r="G4">
-        <v>-0.004330157604604892</v>
+        <v>-0.004330157604604894</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10306,7 +10306,7 @@
         <v>0.8998517245861064</v>
       </c>
       <c r="G5">
-        <v>-0.00433015760114644</v>
+        <v>-0.004330157601146442</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10320,10 +10320,10 @@
         <v>0.02034990983744621</v>
       </c>
       <c r="D6">
-        <v>0.0009575007479215066</v>
+        <v>0.0009575007479215064</v>
       </c>
       <c r="E6">
-        <v>0.006296894770919785</v>
+        <v>0.006296894770919784</v>
       </c>
       <c r="F6">
         <v>0.8993474258594233</v>
@@ -10442,22 +10442,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.04275608209827</v>
+        <v>1.042756082098258</v>
       </c>
       <c r="O2">
-        <v>1.019485521667868</v>
+        <v>1.01948552166781</v>
       </c>
       <c r="P2">
-        <v>1.042154003727713</v>
+        <v>1.04215400372766</v>
       </c>
       <c r="Q2">
-        <v>29.26447752701156</v>
+        <v>29.26447752701105</v>
       </c>
       <c r="R2">
-        <v>-90.03879109617507</v>
+        <v>-90.03879109617672</v>
       </c>
       <c r="S2">
-        <v>150.7169722376497</v>
+        <v>150.7169722376508</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -10501,22 +10501,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.017850815583807</v>
+        <v>1.017850815583789</v>
       </c>
       <c r="O3">
-        <v>0.8902319386659481</v>
+        <v>0.8902319386658908</v>
       </c>
       <c r="P3">
-        <v>1.006968728073418</v>
+        <v>1.006968728073372</v>
       </c>
       <c r="Q3">
-        <v>25.92977054716423</v>
+        <v>25.92977054716383</v>
       </c>
       <c r="R3">
-        <v>-90.77979689235445</v>
+        <v>-90.77979689235561</v>
       </c>
       <c r="S3">
-        <v>153.7687858259478</v>
+        <v>153.7687858259493</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -10560,22 +10560,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9942448483048123</v>
+        <v>0.9942448483047938</v>
       </c>
       <c r="O4">
-        <v>0.8453339436585262</v>
+        <v>0.8453339436584717</v>
       </c>
       <c r="P4">
-        <v>1.01119818510613</v>
+        <v>1.011198185106088</v>
       </c>
       <c r="Q4">
-        <v>25.15127081992832</v>
+        <v>25.15127081992802</v>
       </c>
       <c r="R4">
-        <v>-88.73279947476408</v>
+        <v>-88.7327994747649</v>
       </c>
       <c r="S4">
-        <v>155.2989288465889</v>
+        <v>155.2989288465904</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -10619,22 +10619,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.994244848276962</v>
+        <v>0.9942448482769434</v>
       </c>
       <c r="O5">
-        <v>0.8453339436731188</v>
+        <v>0.8453339436730644</v>
       </c>
       <c r="P5">
-        <v>1.011198185139613</v>
+        <v>1.011198185139571</v>
       </c>
       <c r="Q5">
-        <v>25.15127082109884</v>
+        <v>25.15127082109856</v>
       </c>
       <c r="R5">
-        <v>-88.73279947019721</v>
+        <v>-88.73279947019802</v>
       </c>
       <c r="S5">
-        <v>155.2989288470531</v>
+        <v>155.2989288470545</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -10645,55 +10645,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>34.68462518857657</v>
+        <v>34.68462518857614</v>
       </c>
       <c r="D6">
-        <v>34.68462518857657</v>
+        <v>34.68462518857614</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>8.010071195105743</v>
+        <v>8.010071195105644</v>
       </c>
       <c r="G6">
-        <v>8.010071195105743</v>
+        <v>8.010071195105644</v>
       </c>
       <c r="H6">
-        <v>0.001966667955940062</v>
+        <v>0.001966667954499568</v>
       </c>
       <c r="I6">
-        <v>0.005624308881969514</v>
+        <v>0.005624308881970548</v>
       </c>
       <c r="J6">
-        <v>0.0007385329100565223</v>
+        <v>0.0007385329100564456</v>
       </c>
       <c r="K6">
-        <v>0.006009343834865071</v>
+        <v>0.00600934383486517</v>
       </c>
       <c r="L6">
-        <v>0.0007385329100696446</v>
+        <v>0.0007385329100691217</v>
       </c>
       <c r="M6">
-        <v>0.006009343834854569</v>
+        <v>0.006009343834854746</v>
       </c>
       <c r="N6">
-        <v>0.9093266326766466</v>
+        <v>0.9093266326765918</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9093266326767939</v>
+        <v>0.9093266326768066</v>
       </c>
       <c r="Q6">
-        <v>-4.36595772223275E-12</v>
+        <v>-4.929804196040368E-12</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>-179.9999999999915</v>
+        <v>-179.9999999999892</v>
       </c>
     </row>
   </sheetData>
